--- a/12604997.xlsx
+++ b/12604997.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75B5E309-841A-4853-AAA2-FC7B4397039C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11ADDD02-0A1D-480A-B3AA-0C23C2991666}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="69">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -239,6 +239,9 @@
   </si>
   <si>
     <t>Feeling better</t>
+  </si>
+  <si>
+    <t>Not good</t>
   </si>
 </sst>
 </file>
@@ -1846,48 +1849,96 @@
       </c>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A24" s="13"/>
-      <c r="B24" s="14"/>
-      <c r="C24" s="14"/>
-      <c r="D24" s="14"/>
-      <c r="E24" s="14"/>
-      <c r="F24" s="14"/>
-      <c r="G24" s="14"/>
-      <c r="H24" s="14"/>
-      <c r="I24" s="15" t="str">
+      <c r="A24" s="13">
+        <v>46278</v>
+      </c>
+      <c r="B24" s="14">
+        <v>580</v>
+      </c>
+      <c r="C24" s="14">
+        <v>25</v>
+      </c>
+      <c r="D24" s="14">
+        <v>55</v>
+      </c>
+      <c r="E24" s="14">
+        <v>30</v>
+      </c>
+      <c r="F24" s="14">
+        <v>0</v>
+      </c>
+      <c r="G24" s="14">
+        <v>0</v>
+      </c>
+      <c r="H24" s="14">
+        <v>35</v>
+      </c>
+      <c r="I24" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J24" s="15" t="str">
+        <v>725</v>
+      </c>
+      <c r="J24" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K24" s="16"/>
-      <c r="L24" s="16"/>
-      <c r="M24" s="16"/>
-      <c r="N24" s="17"/>
+        <v>715</v>
+      </c>
+      <c r="K24" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="L24" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="M24" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N24" s="17" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A25" s="13"/>
-      <c r="B25" s="14"/>
-      <c r="C25" s="14"/>
-      <c r="D25" s="14"/>
-      <c r="E25" s="14"/>
-      <c r="F25" s="14"/>
-      <c r="G25" s="14"/>
-      <c r="H25" s="14"/>
-      <c r="I25" s="15" t="str">
+      <c r="A25" s="13">
+        <v>46279</v>
+      </c>
+      <c r="B25" s="14">
+        <v>560</v>
+      </c>
+      <c r="C25" s="14">
+        <v>15</v>
+      </c>
+      <c r="D25" s="14">
+        <v>45</v>
+      </c>
+      <c r="E25" s="14">
+        <v>20</v>
+      </c>
+      <c r="F25" s="14">
+        <v>300</v>
+      </c>
+      <c r="G25" s="14">
+        <v>6</v>
+      </c>
+      <c r="H25" s="14">
+        <v>15</v>
+      </c>
+      <c r="I25" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J25" s="15" t="str">
+        <v>955</v>
+      </c>
+      <c r="J25" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K25" s="16"/>
-      <c r="L25" s="16"/>
-      <c r="M25" s="16"/>
-      <c r="N25" s="17"/>
+        <v>485</v>
+      </c>
+      <c r="K25" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="L25" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="M25" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N25" s="17" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A26" s="13"/>

--- a/12604997.xlsx
+++ b/12604997.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11ADDD02-0A1D-480A-B3AA-0C23C2991666}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6109FA28-8EDC-41A0-8A23-FD98989EE5F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="69">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -1941,26 +1941,50 @@
       </c>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A26" s="13"/>
-      <c r="B26" s="14"/>
-      <c r="C26" s="14"/>
-      <c r="D26" s="14"/>
-      <c r="E26" s="14"/>
-      <c r="F26" s="14"/>
-      <c r="G26" s="14"/>
-      <c r="H26" s="14"/>
-      <c r="I26" s="15" t="str">
+      <c r="A26" s="13">
+        <v>46280</v>
+      </c>
+      <c r="B26" s="14">
+        <v>550</v>
+      </c>
+      <c r="C26" s="14">
+        <v>25</v>
+      </c>
+      <c r="D26" s="14">
+        <v>50</v>
+      </c>
+      <c r="E26" s="14">
+        <v>15</v>
+      </c>
+      <c r="F26" s="14">
+        <v>300</v>
+      </c>
+      <c r="G26" s="14">
+        <v>6</v>
+      </c>
+      <c r="H26" s="14">
+        <v>25</v>
+      </c>
+      <c r="I26" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J26" s="15" t="str">
+        <v>965</v>
+      </c>
+      <c r="J26" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K26" s="16"/>
-      <c r="L26" s="16"/>
-      <c r="M26" s="16"/>
-      <c r="N26" s="17"/>
+        <v>475</v>
+      </c>
+      <c r="K26" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="L26" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="M26" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N26" s="17" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A27" s="13"/>

--- a/12604997.xlsx
+++ b/12604997.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6109FA28-8EDC-41A0-8A23-FD98989EE5F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4C7A6D0-A737-407D-B87B-837F550D0A59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="70">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -242,6 +242,9 @@
   </si>
   <si>
     <t>Not good</t>
+  </si>
+  <si>
+    <t>Average</t>
   </si>
 </sst>
 </file>
@@ -1987,26 +1990,50 @@
       </c>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A27" s="13"/>
-      <c r="B27" s="14"/>
-      <c r="C27" s="14"/>
-      <c r="D27" s="14"/>
-      <c r="E27" s="14"/>
-      <c r="F27" s="14"/>
-      <c r="G27" s="14"/>
-      <c r="H27" s="14"/>
-      <c r="I27" s="15" t="str">
+      <c r="A27" s="13">
+        <v>46281</v>
+      </c>
+      <c r="B27" s="14">
+        <v>580</v>
+      </c>
+      <c r="C27" s="14">
+        <v>15</v>
+      </c>
+      <c r="D27" s="14">
+        <v>40</v>
+      </c>
+      <c r="E27" s="14">
+        <v>25</v>
+      </c>
+      <c r="F27" s="14">
+        <v>300</v>
+      </c>
+      <c r="G27" s="14">
+        <v>6</v>
+      </c>
+      <c r="H27" s="14">
+        <v>25</v>
+      </c>
+      <c r="I27" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J27" s="15" t="str">
+        <v>985</v>
+      </c>
+      <c r="J27" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K27" s="16"/>
-      <c r="L27" s="16"/>
-      <c r="M27" s="16"/>
-      <c r="N27" s="17"/>
+        <v>455</v>
+      </c>
+      <c r="K27" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="L27" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="M27" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N27" s="17" t="s">
+        <v>69</v>
+      </c>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A28" s="13"/>

--- a/12604997.xlsx
+++ b/12604997.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4C7A6D0-A737-407D-B87B-837F550D0A59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45A98B2F-9ABD-4D3A-B082-852BD5781B4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="72">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -245,6 +245,12 @@
   </si>
   <si>
     <t>Average</t>
+  </si>
+  <si>
+    <t>Very Unsatisfied</t>
+  </si>
+  <si>
+    <t>Not Good</t>
   </si>
 </sst>
 </file>
@@ -2036,114 +2042,234 @@
       </c>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A28" s="13"/>
-      <c r="B28" s="14"/>
-      <c r="C28" s="14"/>
-      <c r="D28" s="14"/>
-      <c r="E28" s="14"/>
-      <c r="F28" s="14"/>
-      <c r="G28" s="14"/>
-      <c r="H28" s="14"/>
-      <c r="I28" s="15" t="str">
+      <c r="A28" s="13">
+        <v>46282</v>
+      </c>
+      <c r="B28" s="14">
+        <v>560</v>
+      </c>
+      <c r="C28" s="14">
+        <v>20</v>
+      </c>
+      <c r="D28" s="14">
+        <v>65</v>
+      </c>
+      <c r="E28" s="14">
+        <v>45</v>
+      </c>
+      <c r="F28" s="14">
+        <v>150</v>
+      </c>
+      <c r="G28" s="14">
+        <v>4</v>
+      </c>
+      <c r="H28" s="14">
+        <v>35</v>
+      </c>
+      <c r="I28" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J28" s="15" t="str">
+        <v>875</v>
+      </c>
+      <c r="J28" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K28" s="16"/>
-      <c r="L28" s="16"/>
-      <c r="M28" s="16"/>
-      <c r="N28" s="17"/>
+        <v>565</v>
+      </c>
+      <c r="K28" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="L28" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="M28" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="N28" s="17" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A29" s="13"/>
-      <c r="B29" s="14"/>
-      <c r="C29" s="14"/>
-      <c r="D29" s="14"/>
-      <c r="E29" s="14"/>
-      <c r="F29" s="14"/>
-      <c r="G29" s="14"/>
-      <c r="H29" s="14"/>
-      <c r="I29" s="15" t="str">
+      <c r="A29" s="13">
+        <v>46283</v>
+      </c>
+      <c r="B29" s="14">
+        <v>570</v>
+      </c>
+      <c r="C29" s="14">
+        <v>30</v>
+      </c>
+      <c r="D29" s="14">
+        <v>75</v>
+      </c>
+      <c r="E29" s="14">
+        <v>55</v>
+      </c>
+      <c r="F29" s="14">
+        <v>300</v>
+      </c>
+      <c r="G29" s="14">
+        <v>6</v>
+      </c>
+      <c r="H29" s="14">
+        <v>45</v>
+      </c>
+      <c r="I29" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J29" s="15" t="str">
+        <v>1075</v>
+      </c>
+      <c r="J29" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K29" s="16"/>
-      <c r="L29" s="16"/>
-      <c r="M29" s="16"/>
-      <c r="N29" s="17"/>
+        <v>365</v>
+      </c>
+      <c r="K29" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="L29" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="M29" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="N29" s="17" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A30" s="13"/>
-      <c r="B30" s="14"/>
-      <c r="C30" s="14"/>
-      <c r="D30" s="14"/>
-      <c r="E30" s="14"/>
-      <c r="F30" s="14"/>
-      <c r="G30" s="14"/>
-      <c r="H30" s="14"/>
-      <c r="I30" s="15" t="str">
+      <c r="A30" s="13">
+        <v>46284</v>
+      </c>
+      <c r="B30" s="14">
+        <v>580</v>
+      </c>
+      <c r="C30" s="14">
+        <v>40</v>
+      </c>
+      <c r="D30" s="14">
+        <v>95</v>
+      </c>
+      <c r="E30" s="14">
+        <v>55</v>
+      </c>
+      <c r="F30" s="14">
+        <v>0</v>
+      </c>
+      <c r="G30" s="14">
+        <v>0</v>
+      </c>
+      <c r="H30" s="14">
+        <v>45</v>
+      </c>
+      <c r="I30" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J30" s="15" t="str">
+        <v>815</v>
+      </c>
+      <c r="J30" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K30" s="16"/>
-      <c r="L30" s="16"/>
-      <c r="M30" s="16"/>
-      <c r="N30" s="17"/>
+        <v>625</v>
+      </c>
+      <c r="K30" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="L30" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="M30" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="N30" s="17" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A31" s="13"/>
-      <c r="B31" s="14"/>
-      <c r="C31" s="14"/>
-      <c r="D31" s="14"/>
-      <c r="E31" s="14"/>
-      <c r="F31" s="14"/>
-      <c r="G31" s="14"/>
-      <c r="H31" s="14"/>
-      <c r="I31" s="15" t="str">
+      <c r="A31" s="13">
+        <v>46285</v>
+      </c>
+      <c r="B31" s="14">
+        <v>575</v>
+      </c>
+      <c r="C31" s="14">
+        <v>55</v>
+      </c>
+      <c r="D31" s="14">
+        <v>85</v>
+      </c>
+      <c r="E31" s="14">
+        <v>65</v>
+      </c>
+      <c r="F31" s="14">
+        <v>0</v>
+      </c>
+      <c r="G31" s="14">
+        <v>0</v>
+      </c>
+      <c r="H31" s="14">
+        <v>25</v>
+      </c>
+      <c r="I31" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J31" s="15" t="str">
+        <v>805</v>
+      </c>
+      <c r="J31" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K31" s="16"/>
-      <c r="L31" s="16"/>
-      <c r="M31" s="16"/>
-      <c r="N31" s="17"/>
+        <v>635</v>
+      </c>
+      <c r="K31" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="L31" s="16" t="s">
+        <v>70</v>
+      </c>
+      <c r="M31" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N31" s="17" t="s">
+        <v>71</v>
+      </c>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A32" s="13"/>
-      <c r="B32" s="14"/>
-      <c r="C32" s="14"/>
-      <c r="D32" s="14"/>
-      <c r="E32" s="14"/>
-      <c r="F32" s="14"/>
-      <c r="G32" s="14"/>
-      <c r="H32" s="14"/>
-      <c r="I32" s="15" t="str">
+      <c r="A32" s="13">
+        <v>46286</v>
+      </c>
+      <c r="B32" s="14">
+        <v>555</v>
+      </c>
+      <c r="C32" s="14">
+        <v>45</v>
+      </c>
+      <c r="D32" s="14">
+        <v>75</v>
+      </c>
+      <c r="E32" s="14">
+        <v>35</v>
+      </c>
+      <c r="F32" s="14">
+        <v>300</v>
+      </c>
+      <c r="G32" s="14">
+        <v>6</v>
+      </c>
+      <c r="H32" s="14">
+        <v>55</v>
+      </c>
+      <c r="I32" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J32" s="15" t="str">
+        <v>1065</v>
+      </c>
+      <c r="J32" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K32" s="16"/>
-      <c r="L32" s="16"/>
-      <c r="M32" s="16"/>
-      <c r="N32" s="17"/>
+        <v>375</v>
+      </c>
+      <c r="K32" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="L32" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="M32" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="N32" s="17" t="s">
+        <v>69</v>
+      </c>
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A33" s="13"/>

--- a/12604997.xlsx
+++ b/12604997.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45A98B2F-9ABD-4D3A-B082-852BD5781B4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5DD6F5D9-AD9B-48CA-90E6-FDC15A553E9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="77">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -251,6 +251,21 @@
   </si>
   <si>
     <t>Not Good</t>
+  </si>
+  <si>
+    <t>Excellent</t>
+  </si>
+  <si>
+    <t>Very Satisfied</t>
+  </si>
+  <si>
+    <t>Well</t>
+  </si>
+  <si>
+    <t>Little bit worry</t>
+  </si>
+  <si>
+    <t>try to make it great</t>
   </si>
 </sst>
 </file>
@@ -2272,70 +2287,142 @@
       </c>
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A33" s="13"/>
-      <c r="B33" s="14"/>
-      <c r="C33" s="14"/>
-      <c r="D33" s="14"/>
-      <c r="E33" s="14"/>
-      <c r="F33" s="14"/>
-      <c r="G33" s="14"/>
-      <c r="H33" s="14"/>
-      <c r="I33" s="15" t="str">
+      <c r="A33" s="13">
+        <v>46287</v>
+      </c>
+      <c r="B33" s="14">
+        <v>565</v>
+      </c>
+      <c r="C33" s="14">
+        <v>25</v>
+      </c>
+      <c r="D33" s="14">
+        <v>120</v>
+      </c>
+      <c r="E33" s="14">
+        <v>45</v>
+      </c>
+      <c r="F33" s="14">
+        <v>300</v>
+      </c>
+      <c r="G33" s="14">
+        <v>6</v>
+      </c>
+      <c r="H33" s="14">
+        <v>25</v>
+      </c>
+      <c r="I33" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J33" s="15" t="str">
+        <v>1080</v>
+      </c>
+      <c r="J33" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K33" s="16"/>
-      <c r="L33" s="16"/>
-      <c r="M33" s="16"/>
-      <c r="N33" s="17"/>
+        <v>360</v>
+      </c>
+      <c r="K33" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="L33" s="16" t="s">
+        <v>73</v>
+      </c>
+      <c r="M33" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="N33" s="17" t="s">
+        <v>74</v>
+      </c>
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A34" s="13"/>
-      <c r="B34" s="14"/>
-      <c r="C34" s="14"/>
-      <c r="D34" s="14"/>
-      <c r="E34" s="14"/>
-      <c r="F34" s="14"/>
-      <c r="G34" s="14"/>
-      <c r="H34" s="14"/>
-      <c r="I34" s="15" t="str">
+      <c r="A34" s="13">
+        <v>46288</v>
+      </c>
+      <c r="B34" s="14">
+        <v>485</v>
+      </c>
+      <c r="C34" s="14">
+        <v>45</v>
+      </c>
+      <c r="D34" s="14">
+        <v>80</v>
+      </c>
+      <c r="E34" s="14">
+        <v>60</v>
+      </c>
+      <c r="F34" s="14">
+        <v>250</v>
+      </c>
+      <c r="G34" s="14">
+        <v>5</v>
+      </c>
+      <c r="H34" s="14">
+        <v>35</v>
+      </c>
+      <c r="I34" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J34" s="15" t="str">
+        <v>955</v>
+      </c>
+      <c r="J34" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K34" s="16"/>
-      <c r="L34" s="16"/>
-      <c r="M34" s="16"/>
-      <c r="N34" s="17"/>
+        <v>485</v>
+      </c>
+      <c r="K34" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="L34" s="16" t="s">
+        <v>70</v>
+      </c>
+      <c r="M34" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N34" s="17" t="s">
+        <v>75</v>
+      </c>
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A35" s="13"/>
-      <c r="B35" s="14"/>
-      <c r="C35" s="14"/>
-      <c r="D35" s="14"/>
-      <c r="E35" s="14"/>
-      <c r="F35" s="14"/>
-      <c r="G35" s="14"/>
-      <c r="H35" s="14"/>
-      <c r="I35" s="15" t="str">
+      <c r="A35" s="13">
+        <v>46289</v>
+      </c>
+      <c r="B35" s="14">
+        <v>610</v>
+      </c>
+      <c r="C35" s="14">
+        <v>55</v>
+      </c>
+      <c r="D35" s="14">
+        <v>95</v>
+      </c>
+      <c r="E35" s="14">
+        <v>75</v>
+      </c>
+      <c r="F35" s="14">
+        <v>150</v>
+      </c>
+      <c r="G35" s="14">
+        <v>3</v>
+      </c>
+      <c r="H35" s="14">
+        <v>45</v>
+      </c>
+      <c r="I35" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J35" s="15" t="str">
+        <v>1030</v>
+      </c>
+      <c r="J35" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K35" s="16"/>
-      <c r="L35" s="16"/>
-      <c r="M35" s="16"/>
-      <c r="N35" s="17"/>
+        <v>410</v>
+      </c>
+      <c r="K35" s="16" t="s">
+        <v>72</v>
+      </c>
+      <c r="L35" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="M35" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="N35" s="17" t="s">
+        <v>76</v>
+      </c>
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A36" s="13"/>

--- a/12604997.xlsx
+++ b/12604997.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5DD6F5D9-AD9B-48CA-90E6-FDC15A553E9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB8CDFAA-A486-42F7-9234-72970DE625BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="78">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -266,6 +266,9 @@
   </si>
   <si>
     <t>try to make it great</t>
+  </si>
+  <si>
+    <t>Good feeling better</t>
   </si>
 </sst>
 </file>
@@ -2425,26 +2428,50 @@
       </c>
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A36" s="13"/>
-      <c r="B36" s="14"/>
-      <c r="C36" s="14"/>
-      <c r="D36" s="14"/>
-      <c r="E36" s="14"/>
-      <c r="F36" s="14"/>
-      <c r="G36" s="14"/>
-      <c r="H36" s="14"/>
-      <c r="I36" s="15" t="str">
+      <c r="A36" s="13">
+        <v>46290</v>
+      </c>
+      <c r="B36" s="14">
+        <v>555</v>
+      </c>
+      <c r="C36" s="14">
+        <v>45</v>
+      </c>
+      <c r="D36" s="14">
+        <v>85</v>
+      </c>
+      <c r="E36" s="14">
+        <v>65</v>
+      </c>
+      <c r="F36" s="14">
+        <v>300</v>
+      </c>
+      <c r="G36" s="14">
+        <v>6</v>
+      </c>
+      <c r="H36" s="14">
+        <v>55</v>
+      </c>
+      <c r="I36" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J36" s="15" t="str">
+        <v>1105</v>
+      </c>
+      <c r="J36" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K36" s="16"/>
-      <c r="L36" s="16"/>
-      <c r="M36" s="16"/>
-      <c r="N36" s="17"/>
+        <v>335</v>
+      </c>
+      <c r="K36" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="L36" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="M36" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="N36" s="17" t="s">
+        <v>77</v>
+      </c>
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A37" s="13"/>

--- a/12604997.xlsx
+++ b/12604997.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB8CDFAA-A486-42F7-9234-72970DE625BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37C5C061-3AF5-4333-B2AC-F336CECFF133}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="82">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -269,6 +269,18 @@
   </si>
   <si>
     <t>Good feeling better</t>
+  </si>
+  <si>
+    <t>feeling better</t>
+  </si>
+  <si>
+    <t>feeling great</t>
+  </si>
+  <si>
+    <t>ok good</t>
+  </si>
+  <si>
+    <t>trying to make day great</t>
   </si>
 </sst>
 </file>
@@ -2474,92 +2486,188 @@
       </c>
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A37" s="13"/>
-      <c r="B37" s="14"/>
-      <c r="C37" s="14"/>
-      <c r="D37" s="14"/>
-      <c r="E37" s="14"/>
-      <c r="F37" s="14"/>
-      <c r="G37" s="14"/>
-      <c r="H37" s="14"/>
-      <c r="I37" s="15" t="str">
+      <c r="A37" s="13">
+        <v>46291</v>
+      </c>
+      <c r="B37" s="14">
+        <v>565</v>
+      </c>
+      <c r="C37" s="14">
+        <v>25</v>
+      </c>
+      <c r="D37" s="14">
+        <v>85</v>
+      </c>
+      <c r="E37" s="14">
+        <v>75</v>
+      </c>
+      <c r="F37" s="14">
+        <v>150</v>
+      </c>
+      <c r="G37" s="14">
+        <v>0</v>
+      </c>
+      <c r="H37" s="14">
+        <v>25</v>
+      </c>
+      <c r="I37" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J37" s="15" t="str">
+        <v>925</v>
+      </c>
+      <c r="J37" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K37" s="16"/>
-      <c r="L37" s="16"/>
-      <c r="M37" s="16"/>
-      <c r="N37" s="17"/>
+        <v>515</v>
+      </c>
+      <c r="K37" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="L37" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="M37" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="N37" s="17" t="s">
+        <v>78</v>
+      </c>
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A38" s="13"/>
-      <c r="B38" s="14"/>
-      <c r="C38" s="14"/>
-      <c r="D38" s="14"/>
-      <c r="E38" s="14"/>
-      <c r="F38" s="14"/>
-      <c r="G38" s="14"/>
-      <c r="H38" s="14"/>
-      <c r="I38" s="15" t="str">
+      <c r="A38" s="13">
+        <v>46292</v>
+      </c>
+      <c r="B38" s="14">
+        <v>660</v>
+      </c>
+      <c r="C38" s="14">
+        <v>35</v>
+      </c>
+      <c r="D38" s="14">
+        <v>125</v>
+      </c>
+      <c r="E38" s="14">
+        <v>120</v>
+      </c>
+      <c r="F38" s="14">
+        <v>0</v>
+      </c>
+      <c r="G38" s="14">
+        <v>0</v>
+      </c>
+      <c r="H38" s="14">
+        <v>35</v>
+      </c>
+      <c r="I38" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J38" s="15" t="str">
+        <v>975</v>
+      </c>
+      <c r="J38" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K38" s="16"/>
-      <c r="L38" s="16"/>
-      <c r="M38" s="16"/>
-      <c r="N38" s="17"/>
+        <v>465</v>
+      </c>
+      <c r="K38" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="L38" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="M38" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="N38" s="17" t="s">
+        <v>79</v>
+      </c>
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A39" s="13"/>
-      <c r="B39" s="14"/>
-      <c r="C39" s="14"/>
-      <c r="D39" s="14"/>
-      <c r="E39" s="14"/>
-      <c r="F39" s="14"/>
-      <c r="G39" s="14"/>
-      <c r="H39" s="14"/>
-      <c r="I39" s="15" t="str">
+      <c r="A39" s="13">
+        <v>46293</v>
+      </c>
+      <c r="B39" s="14">
+        <v>620</v>
+      </c>
+      <c r="C39" s="14">
+        <v>15</v>
+      </c>
+      <c r="D39" s="14">
+        <v>180</v>
+      </c>
+      <c r="E39" s="14">
+        <v>90</v>
+      </c>
+      <c r="F39" s="14">
+        <v>0</v>
+      </c>
+      <c r="G39" s="14">
+        <v>0</v>
+      </c>
+      <c r="H39" s="14">
+        <v>45</v>
+      </c>
+      <c r="I39" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J39" s="15" t="str">
+        <v>950</v>
+      </c>
+      <c r="J39" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K39" s="16"/>
-      <c r="L39" s="16"/>
-      <c r="M39" s="16"/>
-      <c r="N39" s="17"/>
+        <v>490</v>
+      </c>
+      <c r="K39" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="L39" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="M39" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N39" s="17" t="s">
+        <v>80</v>
+      </c>
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A40" s="13"/>
-      <c r="B40" s="14"/>
-      <c r="C40" s="14"/>
-      <c r="D40" s="14"/>
-      <c r="E40" s="14"/>
-      <c r="F40" s="14"/>
-      <c r="G40" s="14"/>
-      <c r="H40" s="14"/>
-      <c r="I40" s="15" t="str">
+      <c r="A40" s="13">
+        <v>46294</v>
+      </c>
+      <c r="B40" s="14">
+        <v>600</v>
+      </c>
+      <c r="C40" s="14">
+        <v>5</v>
+      </c>
+      <c r="D40" s="14">
+        <v>200</v>
+      </c>
+      <c r="E40" s="14">
+        <v>230</v>
+      </c>
+      <c r="F40" s="14">
+        <v>0</v>
+      </c>
+      <c r="G40" s="14">
+        <v>0</v>
+      </c>
+      <c r="H40" s="14">
+        <v>30</v>
+      </c>
+      <c r="I40" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J40" s="15" t="str">
+        <v>1065</v>
+      </c>
+      <c r="J40" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K40" s="16"/>
-      <c r="L40" s="16"/>
-      <c r="M40" s="16"/>
-      <c r="N40" s="17"/>
+        <v>375</v>
+      </c>
+      <c r="K40" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="L40" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="M40" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="N40" s="17" t="s">
+        <v>81</v>
+      </c>
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A41" s="13"/>

--- a/12604997.xlsx
+++ b/12604997.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37C5C061-3AF5-4333-B2AC-F336CECFF133}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{448C565B-014F-4F38-B37D-F5A02711BF11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="83">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -281,6 +281,9 @@
   </si>
   <si>
     <t>trying to make day great</t>
+  </si>
+  <si>
+    <t>Good day</t>
   </si>
 </sst>
 </file>
@@ -2670,26 +2673,50 @@
       </c>
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A41" s="13"/>
-      <c r="B41" s="14"/>
-      <c r="C41" s="14"/>
-      <c r="D41" s="14"/>
-      <c r="E41" s="14"/>
-      <c r="F41" s="14"/>
-      <c r="G41" s="14"/>
-      <c r="H41" s="14"/>
-      <c r="I41" s="15" t="str">
+      <c r="A41" s="13">
+        <v>46295</v>
+      </c>
+      <c r="B41" s="14">
+        <v>580</v>
+      </c>
+      <c r="C41" s="14">
+        <v>45</v>
+      </c>
+      <c r="D41" s="14">
+        <v>260</v>
+      </c>
+      <c r="E41" s="14">
+        <v>120</v>
+      </c>
+      <c r="F41" s="14">
+        <v>0</v>
+      </c>
+      <c r="G41" s="14">
+        <v>0</v>
+      </c>
+      <c r="H41" s="14">
+        <v>45</v>
+      </c>
+      <c r="I41" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J41" s="15" t="str">
+        <v>1050</v>
+      </c>
+      <c r="J41" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K41" s="16"/>
-      <c r="L41" s="16"/>
-      <c r="M41" s="16"/>
-      <c r="N41" s="17"/>
+        <v>390</v>
+      </c>
+      <c r="K41" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="L41" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="M41" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="N41" s="17" t="s">
+        <v>82</v>
+      </c>
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A42" s="13"/>

--- a/12604997.xlsx
+++ b/12604997.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{448C565B-014F-4F38-B37D-F5A02711BF11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53475039-0FB5-4CBB-89F1-43FAD3D18C37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="85">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -284,6 +284,12 @@
   </si>
   <si>
     <t>Good day</t>
+  </si>
+  <si>
+    <t>Good Day!</t>
+  </si>
+  <si>
+    <t>Awesome</t>
   </si>
 </sst>
 </file>
@@ -2719,48 +2725,96 @@
       </c>
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A42" s="13"/>
-      <c r="B42" s="14"/>
-      <c r="C42" s="14"/>
-      <c r="D42" s="14"/>
-      <c r="E42" s="14"/>
-      <c r="F42" s="14"/>
-      <c r="G42" s="14"/>
-      <c r="H42" s="14"/>
-      <c r="I42" s="15" t="str">
+      <c r="A42" s="13">
+        <v>46296</v>
+      </c>
+      <c r="B42" s="14">
+        <v>570</v>
+      </c>
+      <c r="C42" s="14">
+        <v>55</v>
+      </c>
+      <c r="D42" s="14">
+        <v>300</v>
+      </c>
+      <c r="E42" s="14">
+        <v>150</v>
+      </c>
+      <c r="F42" s="14">
+        <v>0</v>
+      </c>
+      <c r="G42" s="14">
+        <v>0</v>
+      </c>
+      <c r="H42" s="14">
+        <v>55</v>
+      </c>
+      <c r="I42" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J42" s="15" t="str">
+        <v>1130</v>
+      </c>
+      <c r="J42" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K42" s="16"/>
-      <c r="L42" s="16"/>
-      <c r="M42" s="16"/>
-      <c r="N42" s="17"/>
+        <v>310</v>
+      </c>
+      <c r="K42" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="L42" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="M42" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="N42" s="17" t="s">
+        <v>83</v>
+      </c>
     </row>
     <row r="43" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A43" s="13"/>
-      <c r="B43" s="14"/>
-      <c r="C43" s="14"/>
-      <c r="D43" s="14"/>
-      <c r="E43" s="14"/>
-      <c r="F43" s="14"/>
-      <c r="G43" s="14"/>
-      <c r="H43" s="14"/>
-      <c r="I43" s="15" t="str">
+      <c r="A43" s="13">
+        <v>46297</v>
+      </c>
+      <c r="B43" s="14">
+        <v>600</v>
+      </c>
+      <c r="C43" s="14">
+        <v>65</v>
+      </c>
+      <c r="D43" s="14">
+        <v>320</v>
+      </c>
+      <c r="E43" s="14">
+        <v>140</v>
+      </c>
+      <c r="F43" s="14">
+        <v>0</v>
+      </c>
+      <c r="G43" s="14">
+        <v>0</v>
+      </c>
+      <c r="H43" s="14">
+        <v>75</v>
+      </c>
+      <c r="I43" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J43" s="15" t="str">
+        <v>1200</v>
+      </c>
+      <c r="J43" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K43" s="16"/>
-      <c r="L43" s="16"/>
-      <c r="M43" s="16"/>
-      <c r="N43" s="17"/>
+        <v>240</v>
+      </c>
+      <c r="K43" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="L43" s="16" t="s">
+        <v>73</v>
+      </c>
+      <c r="M43" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="N43" s="17" t="s">
+        <v>84</v>
+      </c>
     </row>
     <row r="44" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A44" s="13"/>

--- a/12604997.xlsx
+++ b/12604997.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53475039-0FB5-4CBB-89F1-43FAD3D18C37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{094FA510-0814-4A57-A7AC-3DC4CC0F8FB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="85">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -2817,26 +2817,50 @@
       </c>
     </row>
     <row r="44" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A44" s="13"/>
-      <c r="B44" s="14"/>
-      <c r="C44" s="14"/>
-      <c r="D44" s="14"/>
-      <c r="E44" s="14"/>
-      <c r="F44" s="14"/>
-      <c r="G44" s="14"/>
-      <c r="H44" s="14"/>
-      <c r="I44" s="15" t="str">
+      <c r="A44" s="13">
+        <v>46298</v>
+      </c>
+      <c r="B44" s="14">
+        <v>620</v>
+      </c>
+      <c r="C44" s="14">
+        <v>75</v>
+      </c>
+      <c r="D44" s="14">
+        <v>340</v>
+      </c>
+      <c r="E44" s="14">
+        <v>150</v>
+      </c>
+      <c r="F44" s="14">
+        <v>0</v>
+      </c>
+      <c r="G44" s="14">
+        <v>0</v>
+      </c>
+      <c r="H44" s="14">
+        <v>65</v>
+      </c>
+      <c r="I44" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J44" s="15" t="str">
+        <v>1250</v>
+      </c>
+      <c r="J44" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K44" s="16"/>
-      <c r="L44" s="16"/>
-      <c r="M44" s="16"/>
-      <c r="N44" s="17"/>
+        <v>190</v>
+      </c>
+      <c r="K44" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="L44" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="M44" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N44" s="17" t="s">
+        <v>69</v>
+      </c>
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A45" s="13"/>

--- a/12604997.xlsx
+++ b/12604997.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{094FA510-0814-4A57-A7AC-3DC4CC0F8FB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC694AF1-6A5A-460E-9B02-EA4662B06C95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="86">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -290,6 +290,9 @@
   </si>
   <si>
     <t>Awesome</t>
+  </si>
+  <si>
+    <t>veryGood</t>
   </si>
 </sst>
 </file>
@@ -2863,48 +2866,96 @@
       </c>
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A45" s="13"/>
-      <c r="B45" s="14"/>
-      <c r="C45" s="14"/>
-      <c r="D45" s="14"/>
-      <c r="E45" s="14"/>
-      <c r="F45" s="14"/>
-      <c r="G45" s="14"/>
-      <c r="H45" s="14"/>
-      <c r="I45" s="15" t="str">
+      <c r="A45" s="13">
+        <v>46299</v>
+      </c>
+      <c r="B45" s="14">
+        <v>590</v>
+      </c>
+      <c r="C45" s="14">
+        <v>85</v>
+      </c>
+      <c r="D45" s="14">
+        <v>360</v>
+      </c>
+      <c r="E45" s="14">
+        <v>120</v>
+      </c>
+      <c r="F45" s="14">
+        <v>0</v>
+      </c>
+      <c r="G45" s="14">
+        <v>0</v>
+      </c>
+      <c r="H45" s="14">
+        <v>55</v>
+      </c>
+      <c r="I45" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J45" s="15" t="str">
+        <v>1210</v>
+      </c>
+      <c r="J45" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K45" s="16"/>
-      <c r="L45" s="16"/>
-      <c r="M45" s="16"/>
-      <c r="N45" s="17"/>
+        <v>230</v>
+      </c>
+      <c r="K45" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="L45" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="M45" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="N45" s="17" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A46" s="13"/>
-      <c r="B46" s="14"/>
-      <c r="C46" s="14"/>
-      <c r="D46" s="14"/>
-      <c r="E46" s="14"/>
-      <c r="F46" s="14"/>
-      <c r="G46" s="14"/>
-      <c r="H46" s="14"/>
-      <c r="I46" s="15" t="str">
+      <c r="A46" s="13">
+        <v>46300</v>
+      </c>
+      <c r="B46" s="14">
+        <v>595</v>
+      </c>
+      <c r="C46" s="14">
+        <v>95</v>
+      </c>
+      <c r="D46" s="14">
+        <v>220</v>
+      </c>
+      <c r="E46" s="14">
+        <v>140</v>
+      </c>
+      <c r="F46" s="14">
+        <v>300</v>
+      </c>
+      <c r="G46" s="14">
+        <v>6</v>
+      </c>
+      <c r="H46" s="14">
+        <v>45</v>
+      </c>
+      <c r="I46" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J46" s="15" t="str">
+        <v>1395</v>
+      </c>
+      <c r="J46" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K46" s="16"/>
-      <c r="L46" s="16"/>
-      <c r="M46" s="16"/>
-      <c r="N46" s="17"/>
+        <v>45</v>
+      </c>
+      <c r="K46" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="L46" s="16" t="s">
+        <v>73</v>
+      </c>
+      <c r="M46" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="N46" s="17" t="s">
+        <v>85</v>
+      </c>
     </row>
     <row r="47" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A47" s="13"/>

--- a/12604997.xlsx
+++ b/12604997.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC694AF1-6A5A-460E-9B02-EA4662B06C95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF31DF03-1394-491D-B08F-FD648108C053}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="86">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -2958,26 +2958,50 @@
       </c>
     </row>
     <row r="47" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A47" s="13"/>
-      <c r="B47" s="14"/>
-      <c r="C47" s="14"/>
-      <c r="D47" s="14"/>
-      <c r="E47" s="14"/>
-      <c r="F47" s="14"/>
-      <c r="G47" s="14"/>
-      <c r="H47" s="14"/>
-      <c r="I47" s="15" t="str">
+      <c r="A47" s="13">
+        <v>46301</v>
+      </c>
+      <c r="B47" s="14">
+        <v>680</v>
+      </c>
+      <c r="C47" s="14">
+        <v>25</v>
+      </c>
+      <c r="D47" s="14">
+        <v>230</v>
+      </c>
+      <c r="E47" s="14">
+        <v>70</v>
+      </c>
+      <c r="F47" s="14">
+        <v>300</v>
+      </c>
+      <c r="G47" s="14">
+        <v>6</v>
+      </c>
+      <c r="H47" s="14">
+        <v>35</v>
+      </c>
+      <c r="I47" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J47" s="15" t="str">
+        <v>1340</v>
+      </c>
+      <c r="J47" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K47" s="16"/>
-      <c r="L47" s="16"/>
-      <c r="M47" s="16"/>
-      <c r="N47" s="17"/>
+        <v>100</v>
+      </c>
+      <c r="K47" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="L47" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="M47" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="N47" s="17" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A48" s="13"/>

--- a/12604997.xlsx
+++ b/12604997.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF31DF03-1394-491D-B08F-FD648108C053}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98B5B45D-8312-402A-BD39-2EAD12A0BACB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="86">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -3004,70 +3004,142 @@
       </c>
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A48" s="13"/>
-      <c r="B48" s="14"/>
-      <c r="C48" s="14"/>
-      <c r="D48" s="14"/>
-      <c r="E48" s="14"/>
-      <c r="F48" s="14"/>
-      <c r="G48" s="14"/>
-      <c r="H48" s="14"/>
-      <c r="I48" s="15" t="str">
+      <c r="A48" s="13">
+        <v>46302</v>
+      </c>
+      <c r="B48" s="14">
+        <v>620</v>
+      </c>
+      <c r="C48" s="14">
+        <v>20</v>
+      </c>
+      <c r="D48" s="14">
+        <v>200</v>
+      </c>
+      <c r="E48" s="14">
+        <v>65</v>
+      </c>
+      <c r="F48" s="14">
+        <v>400</v>
+      </c>
+      <c r="G48" s="14">
+        <v>8</v>
+      </c>
+      <c r="H48" s="14">
+        <v>35</v>
+      </c>
+      <c r="I48" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J48" s="15" t="str">
+        <v>1340</v>
+      </c>
+      <c r="J48" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K48" s="16"/>
-      <c r="L48" s="16"/>
-      <c r="M48" s="16"/>
-      <c r="N48" s="17"/>
+        <v>100</v>
+      </c>
+      <c r="K48" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="L48" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="M48" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="N48" s="17" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A49" s="13"/>
-      <c r="B49" s="14"/>
-      <c r="C49" s="14"/>
-      <c r="D49" s="14"/>
-      <c r="E49" s="14"/>
-      <c r="F49" s="14"/>
-      <c r="G49" s="14"/>
-      <c r="H49" s="14"/>
-      <c r="I49" s="15" t="str">
+      <c r="A49" s="13">
+        <v>46303</v>
+      </c>
+      <c r="B49" s="14">
+        <v>580</v>
+      </c>
+      <c r="C49" s="14">
+        <v>30</v>
+      </c>
+      <c r="D49" s="14">
+        <v>180</v>
+      </c>
+      <c r="E49" s="14">
+        <v>45</v>
+      </c>
+      <c r="F49" s="14">
+        <v>0</v>
+      </c>
+      <c r="G49" s="14">
+        <v>0</v>
+      </c>
+      <c r="H49" s="14">
+        <v>45</v>
+      </c>
+      <c r="I49" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J49" s="15" t="str">
+        <v>880</v>
+      </c>
+      <c r="J49" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K49" s="16"/>
-      <c r="L49" s="16"/>
-      <c r="M49" s="16"/>
-      <c r="N49" s="17"/>
+        <v>560</v>
+      </c>
+      <c r="K49" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="L49" s="16" t="s">
+        <v>73</v>
+      </c>
+      <c r="M49" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="N49" s="17" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A50" s="13"/>
-      <c r="B50" s="14"/>
-      <c r="C50" s="14"/>
-      <c r="D50" s="14"/>
-      <c r="E50" s="14"/>
-      <c r="F50" s="14"/>
-      <c r="G50" s="14"/>
-      <c r="H50" s="14"/>
-      <c r="I50" s="15" t="str">
+      <c r="A50" s="13">
+        <v>46304</v>
+      </c>
+      <c r="B50" s="14">
+        <v>550</v>
+      </c>
+      <c r="C50" s="14">
+        <v>40</v>
+      </c>
+      <c r="D50" s="14">
+        <v>240</v>
+      </c>
+      <c r="E50" s="14">
+        <v>55</v>
+      </c>
+      <c r="F50" s="14">
+        <v>0</v>
+      </c>
+      <c r="G50" s="14">
+        <v>0</v>
+      </c>
+      <c r="H50" s="14">
+        <v>55</v>
+      </c>
+      <c r="I50" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J50" s="15" t="str">
+        <v>940</v>
+      </c>
+      <c r="J50" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K50" s="16"/>
-      <c r="L50" s="16"/>
-      <c r="M50" s="16"/>
-      <c r="N50" s="17"/>
+        <v>500</v>
+      </c>
+      <c r="K50" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="L50" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="M50" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N50" s="17" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="51" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A51" s="13"/>

--- a/12604997.xlsx
+++ b/12604997.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98B5B45D-8312-402A-BD39-2EAD12A0BACB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E579CFB-4816-40AC-90E2-2B299DC69B0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="241" uniqueCount="86">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -3142,48 +3142,96 @@
       </c>
     </row>
     <row r="51" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A51" s="13"/>
-      <c r="B51" s="14"/>
-      <c r="C51" s="14"/>
-      <c r="D51" s="14"/>
-      <c r="E51" s="14"/>
-      <c r="F51" s="14"/>
-      <c r="G51" s="14"/>
-      <c r="H51" s="14"/>
-      <c r="I51" s="15" t="str">
+      <c r="A51" s="13">
+        <v>46305</v>
+      </c>
+      <c r="B51" s="14">
+        <v>560</v>
+      </c>
+      <c r="C51" s="14">
+        <v>45</v>
+      </c>
+      <c r="D51" s="14">
+        <v>200</v>
+      </c>
+      <c r="E51" s="14">
+        <v>45</v>
+      </c>
+      <c r="F51" s="14">
+        <v>0</v>
+      </c>
+      <c r="G51" s="14">
+        <v>0</v>
+      </c>
+      <c r="H51" s="14">
+        <v>65</v>
+      </c>
+      <c r="I51" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J51" s="15" t="str">
+        <v>915</v>
+      </c>
+      <c r="J51" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K51" s="16"/>
-      <c r="L51" s="16"/>
-      <c r="M51" s="16"/>
-      <c r="N51" s="17"/>
+        <v>525</v>
+      </c>
+      <c r="K51" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="L51" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="M51" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="N51" s="17" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="52" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A52" s="13"/>
-      <c r="B52" s="14"/>
-      <c r="C52" s="14"/>
-      <c r="D52" s="14"/>
-      <c r="E52" s="14"/>
-      <c r="F52" s="14"/>
-      <c r="G52" s="14"/>
-      <c r="H52" s="14"/>
-      <c r="I52" s="15" t="str">
+      <c r="A52" s="13">
+        <v>46306</v>
+      </c>
+      <c r="B52" s="14">
+        <v>580</v>
+      </c>
+      <c r="C52" s="14">
+        <v>55</v>
+      </c>
+      <c r="D52" s="14">
+        <v>250</v>
+      </c>
+      <c r="E52" s="14">
+        <v>55</v>
+      </c>
+      <c r="F52" s="14">
+        <v>0</v>
+      </c>
+      <c r="G52" s="14">
+        <v>0</v>
+      </c>
+      <c r="H52" s="14">
+        <v>75</v>
+      </c>
+      <c r="I52" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J52" s="15" t="str">
+        <v>1015</v>
+      </c>
+      <c r="J52" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K52" s="16"/>
-      <c r="L52" s="16"/>
-      <c r="M52" s="16"/>
-      <c r="N52" s="17"/>
+        <v>425</v>
+      </c>
+      <c r="K52" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="L52" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="M52" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="N52" s="17" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="53" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A53" s="13"/>

--- a/12604997.xlsx
+++ b/12604997.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E579CFB-4816-40AC-90E2-2B299DC69B0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F85D2B7B-FF3F-4421-ACC6-6B001A9912FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="241" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="261" uniqueCount="86">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -3234,114 +3234,234 @@
       </c>
     </row>
     <row r="53" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A53" s="13"/>
-      <c r="B53" s="14"/>
-      <c r="C53" s="14"/>
-      <c r="D53" s="14"/>
-      <c r="E53" s="14"/>
-      <c r="F53" s="14"/>
-      <c r="G53" s="14"/>
-      <c r="H53" s="14"/>
-      <c r="I53" s="15" t="str">
+      <c r="A53" s="13">
+        <v>46307</v>
+      </c>
+      <c r="B53" s="14">
+        <v>565</v>
+      </c>
+      <c r="C53" s="14">
+        <v>45</v>
+      </c>
+      <c r="D53" s="14">
+        <v>300</v>
+      </c>
+      <c r="E53" s="14">
+        <v>85</v>
+      </c>
+      <c r="F53" s="14">
+        <v>0</v>
+      </c>
+      <c r="G53" s="14">
+        <v>0</v>
+      </c>
+      <c r="H53" s="14">
+        <v>75</v>
+      </c>
+      <c r="I53" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J53" s="15" t="str">
+        <v>1070</v>
+      </c>
+      <c r="J53" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K53" s="16"/>
-      <c r="L53" s="16"/>
-      <c r="M53" s="16"/>
-      <c r="N53" s="17"/>
+        <v>370</v>
+      </c>
+      <c r="K53" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="L53" s="16" t="s">
+        <v>73</v>
+      </c>
+      <c r="M53" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N53" s="17" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="54" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A54" s="13"/>
-      <c r="B54" s="14"/>
-      <c r="C54" s="14"/>
-      <c r="D54" s="14"/>
-      <c r="E54" s="14"/>
-      <c r="F54" s="14"/>
-      <c r="G54" s="14"/>
-      <c r="H54" s="14"/>
-      <c r="I54" s="15" t="str">
+      <c r="A54" s="13">
+        <v>46308</v>
+      </c>
+      <c r="B54" s="14">
+        <v>600</v>
+      </c>
+      <c r="C54" s="14">
+        <v>65</v>
+      </c>
+      <c r="D54" s="14">
+        <v>280</v>
+      </c>
+      <c r="E54" s="14">
+        <v>95</v>
+      </c>
+      <c r="F54" s="14">
+        <v>0</v>
+      </c>
+      <c r="G54" s="14">
+        <v>0</v>
+      </c>
+      <c r="H54" s="14">
+        <v>125</v>
+      </c>
+      <c r="I54" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J54" s="15" t="str">
+        <v>1165</v>
+      </c>
+      <c r="J54" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K54" s="16"/>
-      <c r="L54" s="16"/>
-      <c r="M54" s="16"/>
-      <c r="N54" s="17"/>
+        <v>275</v>
+      </c>
+      <c r="K54" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="L54" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="M54" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="N54" s="17" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="55" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A55" s="13"/>
-      <c r="B55" s="14"/>
-      <c r="C55" s="14"/>
-      <c r="D55" s="14"/>
-      <c r="E55" s="14"/>
-      <c r="F55" s="14"/>
-      <c r="G55" s="14"/>
-      <c r="H55" s="14"/>
-      <c r="I55" s="15" t="str">
+      <c r="A55" s="13">
+        <v>46309</v>
+      </c>
+      <c r="B55" s="14">
+        <v>555</v>
+      </c>
+      <c r="C55" s="14">
+        <v>75</v>
+      </c>
+      <c r="D55" s="14">
+        <v>320</v>
+      </c>
+      <c r="E55" s="14">
+        <v>65</v>
+      </c>
+      <c r="F55" s="14">
+        <v>0</v>
+      </c>
+      <c r="G55" s="14">
+        <v>0</v>
+      </c>
+      <c r="H55" s="14">
+        <v>145</v>
+      </c>
+      <c r="I55" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J55" s="15" t="str">
+        <v>1160</v>
+      </c>
+      <c r="J55" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K55" s="16"/>
-      <c r="L55" s="16"/>
-      <c r="M55" s="16"/>
-      <c r="N55" s="17"/>
+        <v>280</v>
+      </c>
+      <c r="K55" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="L55" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="M55" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="N55" s="17" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="56" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A56" s="13"/>
-      <c r="B56" s="14"/>
-      <c r="C56" s="14"/>
-      <c r="D56" s="14"/>
-      <c r="E56" s="14"/>
-      <c r="F56" s="14"/>
-      <c r="G56" s="14"/>
-      <c r="H56" s="14"/>
-      <c r="I56" s="15" t="str">
+      <c r="A56" s="13">
+        <v>46310</v>
+      </c>
+      <c r="B56" s="14">
+        <v>585</v>
+      </c>
+      <c r="C56" s="14">
+        <v>85</v>
+      </c>
+      <c r="D56" s="14">
+        <v>340</v>
+      </c>
+      <c r="E56" s="14">
+        <v>75</v>
+      </c>
+      <c r="F56" s="14">
+        <v>0</v>
+      </c>
+      <c r="G56" s="14">
+        <v>0</v>
+      </c>
+      <c r="H56" s="14">
+        <v>155</v>
+      </c>
+      <c r="I56" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J56" s="15" t="str">
+        <v>1240</v>
+      </c>
+      <c r="J56" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K56" s="16"/>
-      <c r="L56" s="16"/>
-      <c r="M56" s="16"/>
-      <c r="N56" s="17"/>
+        <v>200</v>
+      </c>
+      <c r="K56" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="L56" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="M56" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="N56" s="17" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="57" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A57" s="13"/>
-      <c r="B57" s="14"/>
-      <c r="C57" s="14"/>
-      <c r="D57" s="14"/>
-      <c r="E57" s="14"/>
-      <c r="F57" s="14"/>
-      <c r="G57" s="14"/>
-      <c r="H57" s="14"/>
-      <c r="I57" s="15" t="str">
+      <c r="A57" s="13">
+        <v>46311</v>
+      </c>
+      <c r="B57" s="14">
+        <v>575</v>
+      </c>
+      <c r="C57" s="14">
+        <v>55</v>
+      </c>
+      <c r="D57" s="14">
+        <v>280</v>
+      </c>
+      <c r="E57" s="14">
+        <v>55</v>
+      </c>
+      <c r="F57" s="14">
+        <v>0</v>
+      </c>
+      <c r="G57" s="14">
+        <v>0</v>
+      </c>
+      <c r="H57" s="14">
+        <v>95</v>
+      </c>
+      <c r="I57" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J57" s="15" t="str">
+        <v>1060</v>
+      </c>
+      <c r="J57" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K57" s="16"/>
-      <c r="L57" s="16"/>
-      <c r="M57" s="16"/>
-      <c r="N57" s="17"/>
+        <v>380</v>
+      </c>
+      <c r="K57" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="L57" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="M57" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N57" s="17" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="58" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A58" s="13"/>

--- a/12604997.xlsx
+++ b/12604997.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F85D2B7B-FF3F-4421-ACC6-6B001A9912FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{206BBA0E-E54C-4618-B468-176CEDA55882}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="261" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="273" uniqueCount="86">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -3464,70 +3464,142 @@
       </c>
     </row>
     <row r="58" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A58" s="13"/>
-      <c r="B58" s="14"/>
-      <c r="C58" s="14"/>
-      <c r="D58" s="14"/>
-      <c r="E58" s="14"/>
-      <c r="F58" s="14"/>
-      <c r="G58" s="14"/>
-      <c r="H58" s="14"/>
-      <c r="I58" s="15" t="str">
+      <c r="A58" s="13">
+        <v>46312</v>
+      </c>
+      <c r="B58" s="14">
+        <v>555</v>
+      </c>
+      <c r="C58" s="14">
+        <v>85</v>
+      </c>
+      <c r="D58" s="14">
+        <v>340</v>
+      </c>
+      <c r="E58" s="14">
+        <v>95</v>
+      </c>
+      <c r="F58" s="14">
+        <v>0</v>
+      </c>
+      <c r="G58" s="14">
+        <v>0</v>
+      </c>
+      <c r="H58" s="14">
+        <v>55</v>
+      </c>
+      <c r="I58" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J58" s="15" t="str">
+        <v>1130</v>
+      </c>
+      <c r="J58" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K58" s="16"/>
-      <c r="L58" s="16"/>
-      <c r="M58" s="16"/>
-      <c r="N58" s="17"/>
+        <v>310</v>
+      </c>
+      <c r="K58" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="L58" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="M58" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N58" s="17" t="s">
+        <v>69</v>
+      </c>
     </row>
     <row r="59" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A59" s="13"/>
-      <c r="B59" s="14"/>
-      <c r="C59" s="14"/>
-      <c r="D59" s="14"/>
-      <c r="E59" s="14"/>
-      <c r="F59" s="14"/>
-      <c r="G59" s="14"/>
-      <c r="H59" s="14"/>
-      <c r="I59" s="15" t="str">
+      <c r="A59" s="13">
+        <v>46313</v>
+      </c>
+      <c r="B59" s="14">
+        <v>565</v>
+      </c>
+      <c r="C59" s="14">
+        <v>65</v>
+      </c>
+      <c r="D59" s="14">
+        <v>245</v>
+      </c>
+      <c r="E59" s="14">
+        <v>75</v>
+      </c>
+      <c r="F59" s="14">
+        <v>0</v>
+      </c>
+      <c r="G59" s="14">
+        <v>0</v>
+      </c>
+      <c r="H59" s="14">
+        <v>65</v>
+      </c>
+      <c r="I59" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J59" s="15" t="str">
+        <v>1015</v>
+      </c>
+      <c r="J59" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K59" s="16"/>
-      <c r="L59" s="16"/>
-      <c r="M59" s="16"/>
-      <c r="N59" s="17"/>
+        <v>425</v>
+      </c>
+      <c r="K59" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="L59" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="M59" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="N59" s="17" t="s">
+        <v>69</v>
+      </c>
     </row>
     <row r="60" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A60" s="13"/>
-      <c r="B60" s="14"/>
-      <c r="C60" s="14"/>
-      <c r="D60" s="14"/>
-      <c r="E60" s="14"/>
-      <c r="F60" s="14"/>
-      <c r="G60" s="14"/>
-      <c r="H60" s="14"/>
-      <c r="I60" s="15" t="str">
+      <c r="A60" s="13">
+        <v>46314</v>
+      </c>
+      <c r="B60" s="14">
+        <v>665</v>
+      </c>
+      <c r="C60" s="14">
+        <v>45</v>
+      </c>
+      <c r="D60" s="14">
+        <v>190</v>
+      </c>
+      <c r="E60" s="14">
+        <v>65</v>
+      </c>
+      <c r="F60" s="14">
+        <v>0</v>
+      </c>
+      <c r="G60" s="14">
+        <v>0</v>
+      </c>
+      <c r="H60" s="14">
+        <v>75</v>
+      </c>
+      <c r="I60" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J60" s="15" t="str">
+        <v>1040</v>
+      </c>
+      <c r="J60" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K60" s="16"/>
-      <c r="L60" s="16"/>
-      <c r="M60" s="16"/>
-      <c r="N60" s="17"/>
+        <v>400</v>
+      </c>
+      <c r="K60" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="L60" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="M60" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N60" s="17" t="s">
+        <v>69</v>
+      </c>
     </row>
     <row r="61" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A61" s="13"/>

--- a/12604997.xlsx
+++ b/12604997.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{206BBA0E-E54C-4618-B468-176CEDA55882}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4AF851C-237B-424D-A4B4-C98BE3994EBF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="273" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="86">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -3602,70 +3602,142 @@
       </c>
     </row>
     <row r="61" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A61" s="13"/>
-      <c r="B61" s="14"/>
-      <c r="C61" s="14"/>
-      <c r="D61" s="14"/>
-      <c r="E61" s="14"/>
-      <c r="F61" s="14"/>
-      <c r="G61" s="14"/>
-      <c r="H61" s="14"/>
-      <c r="I61" s="15" t="str">
+      <c r="A61" s="13">
+        <v>46315</v>
+      </c>
+      <c r="B61" s="14">
+        <v>675</v>
+      </c>
+      <c r="C61" s="14">
+        <v>45</v>
+      </c>
+      <c r="D61" s="14">
+        <v>200</v>
+      </c>
+      <c r="E61" s="14">
+        <v>110</v>
+      </c>
+      <c r="F61" s="14">
+        <v>0</v>
+      </c>
+      <c r="G61" s="14">
+        <v>0</v>
+      </c>
+      <c r="H61" s="14">
+        <v>55</v>
+      </c>
+      <c r="I61" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J61" s="15" t="str">
+        <v>1085</v>
+      </c>
+      <c r="J61" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K61" s="16"/>
-      <c r="L61" s="16"/>
-      <c r="M61" s="16"/>
-      <c r="N61" s="17"/>
+        <v>355</v>
+      </c>
+      <c r="K61" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="L61" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="M61" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="N61" s="17" t="s">
+        <v>69</v>
+      </c>
     </row>
     <row r="62" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A62" s="13"/>
-      <c r="B62" s="14"/>
-      <c r="C62" s="14"/>
-      <c r="D62" s="14"/>
-      <c r="E62" s="14"/>
-      <c r="F62" s="14"/>
-      <c r="G62" s="14"/>
-      <c r="H62" s="14"/>
-      <c r="I62" s="15" t="str">
+      <c r="A62" s="13">
+        <v>46316</v>
+      </c>
+      <c r="B62" s="14">
+        <v>685</v>
+      </c>
+      <c r="C62" s="14">
+        <v>35</v>
+      </c>
+      <c r="D62" s="14">
+        <v>180</v>
+      </c>
+      <c r="E62" s="14">
+        <v>125</v>
+      </c>
+      <c r="F62" s="14">
+        <v>300</v>
+      </c>
+      <c r="G62" s="14">
+        <v>6</v>
+      </c>
+      <c r="H62" s="14">
+        <v>45</v>
+      </c>
+      <c r="I62" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J62" s="15" t="str">
+        <v>1370</v>
+      </c>
+      <c r="J62" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K62" s="16"/>
-      <c r="L62" s="16"/>
-      <c r="M62" s="16"/>
-      <c r="N62" s="17"/>
+        <v>70</v>
+      </c>
+      <c r="K62" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="L62" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="M62" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="N62" s="17" t="s">
+        <v>69</v>
+      </c>
     </row>
     <row r="63" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A63" s="13"/>
-      <c r="B63" s="14"/>
-      <c r="C63" s="14"/>
-      <c r="D63" s="14"/>
-      <c r="E63" s="14"/>
-      <c r="F63" s="14"/>
-      <c r="G63" s="14"/>
-      <c r="H63" s="14"/>
-      <c r="I63" s="15" t="str">
+      <c r="A63" s="13">
+        <v>46317</v>
+      </c>
+      <c r="B63" s="14">
+        <v>690</v>
+      </c>
+      <c r="C63" s="14">
+        <v>25</v>
+      </c>
+      <c r="D63" s="14">
+        <v>175</v>
+      </c>
+      <c r="E63" s="14">
+        <v>95</v>
+      </c>
+      <c r="F63" s="14">
+        <v>150</v>
+      </c>
+      <c r="G63" s="14">
+        <v>3</v>
+      </c>
+      <c r="H63" s="14">
+        <v>35</v>
+      </c>
+      <c r="I63" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J63" s="15" t="str">
+        <v>1170</v>
+      </c>
+      <c r="J63" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K63" s="16"/>
-      <c r="L63" s="16"/>
-      <c r="M63" s="16"/>
-      <c r="N63" s="17"/>
+        <v>270</v>
+      </c>
+      <c r="K63" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="L63" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="M63" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="N63" s="17" t="s">
+        <v>69</v>
+      </c>
     </row>
     <row r="64" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A64" s="13"/>

--- a/12604997.xlsx
+++ b/12604997.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4AF851C-237B-424D-A4B4-C98BE3994EBF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2AC700A-13B3-4416-9CB9-C16A46258378}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="293" uniqueCount="87">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -293,6 +293,9 @@
   </si>
   <si>
     <t>veryGood</t>
+  </si>
+  <si>
+    <t>Normal Day</t>
   </si>
 </sst>
 </file>
@@ -3740,48 +3743,96 @@
       </c>
     </row>
     <row r="64" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A64" s="13"/>
-      <c r="B64" s="14"/>
-      <c r="C64" s="14"/>
-      <c r="D64" s="14"/>
-      <c r="E64" s="14"/>
-      <c r="F64" s="14"/>
-      <c r="G64" s="14"/>
-      <c r="H64" s="14"/>
-      <c r="I64" s="15" t="str">
+      <c r="A64" s="13">
+        <v>46318</v>
+      </c>
+      <c r="B64" s="14">
+        <v>650</v>
+      </c>
+      <c r="C64" s="14">
+        <v>85</v>
+      </c>
+      <c r="D64" s="14">
+        <v>125</v>
+      </c>
+      <c r="E64" s="14">
+        <v>75</v>
+      </c>
+      <c r="F64" s="14">
+        <v>300</v>
+      </c>
+      <c r="G64" s="14">
+        <v>6</v>
+      </c>
+      <c r="H64" s="14">
+        <v>25</v>
+      </c>
+      <c r="I64" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J64" s="15" t="str">
+        <v>1260</v>
+      </c>
+      <c r="J64" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K64" s="16"/>
-      <c r="L64" s="16"/>
-      <c r="M64" s="16"/>
-      <c r="N64" s="17"/>
+        <v>180</v>
+      </c>
+      <c r="K64" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="L64" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="M64" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="N64" s="17" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="65" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A65" s="13"/>
-      <c r="B65" s="14"/>
-      <c r="C65" s="14"/>
-      <c r="D65" s="14"/>
-      <c r="E65" s="14"/>
-      <c r="F65" s="14"/>
-      <c r="G65" s="14"/>
-      <c r="H65" s="14"/>
-      <c r="I65" s="15" t="str">
+      <c r="A65" s="13">
+        <v>46319</v>
+      </c>
+      <c r="B65" s="14">
+        <v>660</v>
+      </c>
+      <c r="C65" s="14">
+        <v>45</v>
+      </c>
+      <c r="D65" s="14">
+        <v>120</v>
+      </c>
+      <c r="E65" s="14">
+        <v>85</v>
+      </c>
+      <c r="F65" s="14">
+        <v>100</v>
+      </c>
+      <c r="G65" s="14">
+        <v>2</v>
+      </c>
+      <c r="H65" s="14">
+        <v>45</v>
+      </c>
+      <c r="I65" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J65" s="15" t="str">
+        <v>1055</v>
+      </c>
+      <c r="J65" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K65" s="16"/>
-      <c r="L65" s="16"/>
-      <c r="M65" s="16"/>
-      <c r="N65" s="17"/>
+        <v>385</v>
+      </c>
+      <c r="K65" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="L65" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="M65" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N65" s="17" t="s">
+        <v>86</v>
+      </c>
     </row>
     <row r="66" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A66" s="13"/>

--- a/12604997.xlsx
+++ b/12604997.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2AC700A-13B3-4416-9CB9-C16A46258378}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EAA2E9CE-D465-4E43-83A7-AF9BB5FE9A21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="293" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="301" uniqueCount="89">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -296,6 +296,12 @@
   </si>
   <si>
     <t>Normal Day</t>
+  </si>
+  <si>
+    <t>Average Day</t>
+  </si>
+  <si>
+    <t>Sunny Day</t>
   </si>
 </sst>
 </file>
@@ -3835,48 +3841,96 @@
       </c>
     </row>
     <row r="66" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A66" s="13"/>
-      <c r="B66" s="14"/>
-      <c r="C66" s="14"/>
-      <c r="D66" s="14"/>
-      <c r="E66" s="14"/>
-      <c r="F66" s="14"/>
-      <c r="G66" s="14"/>
-      <c r="H66" s="14"/>
-      <c r="I66" s="15" t="str">
+      <c r="A66" s="13">
+        <v>46320</v>
+      </c>
+      <c r="B66" s="14">
+        <v>680</v>
+      </c>
+      <c r="C66" s="14">
+        <v>65</v>
+      </c>
+      <c r="D66" s="14">
+        <v>150</v>
+      </c>
+      <c r="E66" s="14">
+        <v>75</v>
+      </c>
+      <c r="F66" s="14">
+        <v>100</v>
+      </c>
+      <c r="G66" s="14">
+        <v>0</v>
+      </c>
+      <c r="H66" s="14">
+        <v>55</v>
+      </c>
+      <c r="I66" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J66" s="15" t="str">
+        <v>1125</v>
+      </c>
+      <c r="J66" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K66" s="16"/>
-      <c r="L66" s="16"/>
-      <c r="M66" s="16"/>
-      <c r="N66" s="17"/>
+        <v>315</v>
+      </c>
+      <c r="K66" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="L66" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="M66" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="N66" s="17" t="s">
+        <v>87</v>
+      </c>
     </row>
     <row r="67" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A67" s="13"/>
-      <c r="B67" s="14"/>
-      <c r="C67" s="14"/>
-      <c r="D67" s="14"/>
-      <c r="E67" s="14"/>
-      <c r="F67" s="14"/>
-      <c r="G67" s="14"/>
-      <c r="H67" s="14"/>
-      <c r="I67" s="15" t="str">
+      <c r="A67" s="13">
+        <v>46321</v>
+      </c>
+      <c r="B67" s="14">
+        <v>570</v>
+      </c>
+      <c r="C67" s="14">
+        <v>55</v>
+      </c>
+      <c r="D67" s="14">
+        <v>180</v>
+      </c>
+      <c r="E67" s="14">
+        <v>95</v>
+      </c>
+      <c r="F67" s="14">
+        <v>120</v>
+      </c>
+      <c r="G67" s="14">
+        <v>0</v>
+      </c>
+      <c r="H67" s="14">
+        <v>65</v>
+      </c>
+      <c r="I67" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J67" s="15" t="str">
+        <v>1085</v>
+      </c>
+      <c r="J67" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K67" s="16"/>
-      <c r="L67" s="16"/>
-      <c r="M67" s="16"/>
-      <c r="N67" s="17"/>
+        <v>355</v>
+      </c>
+      <c r="K67" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="L67" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="M67" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="N67" s="17" t="s">
+        <v>88</v>
+      </c>
     </row>
     <row r="68" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A68" s="13"/>

--- a/12604997.xlsx
+++ b/12604997.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EAA2E9CE-D465-4E43-83A7-AF9BB5FE9A21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26C19B48-926D-4A16-9151-3B4E378B5B65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="301" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="313" uniqueCount="90">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -302,6 +302,9 @@
   </si>
   <si>
     <t>Sunny Day</t>
+  </si>
+  <si>
+    <t>Normal</t>
   </si>
 </sst>
 </file>
@@ -3933,70 +3936,142 @@
       </c>
     </row>
     <row r="68" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A68" s="13"/>
-      <c r="B68" s="14"/>
-      <c r="C68" s="14"/>
-      <c r="D68" s="14"/>
-      <c r="E68" s="14"/>
-      <c r="F68" s="14"/>
-      <c r="G68" s="14"/>
-      <c r="H68" s="14"/>
-      <c r="I68" s="15" t="str">
+      <c r="A68" s="13">
+        <v>46322</v>
+      </c>
+      <c r="B68" s="14">
+        <v>550</v>
+      </c>
+      <c r="C68" s="14">
+        <v>45</v>
+      </c>
+      <c r="D68" s="14">
+        <v>120</v>
+      </c>
+      <c r="E68" s="14">
+        <v>85</v>
+      </c>
+      <c r="F68" s="14">
+        <v>250</v>
+      </c>
+      <c r="G68" s="14">
+        <v>5</v>
+      </c>
+      <c r="H68" s="14">
+        <v>55</v>
+      </c>
+      <c r="I68" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J68" s="15" t="str">
+        <v>1105</v>
+      </c>
+      <c r="J68" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K68" s="16"/>
-      <c r="L68" s="16"/>
-      <c r="M68" s="16"/>
-      <c r="N68" s="17"/>
+        <v>335</v>
+      </c>
+      <c r="K68" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="L68" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="M68" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="N68" s="17" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="69" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A69" s="13"/>
-      <c r="B69" s="14"/>
-      <c r="C69" s="14"/>
-      <c r="D69" s="14"/>
-      <c r="E69" s="14"/>
-      <c r="F69" s="14"/>
-      <c r="G69" s="14"/>
-      <c r="H69" s="14"/>
-      <c r="I69" s="15" t="str">
+      <c r="A69" s="13">
+        <v>46323</v>
+      </c>
+      <c r="B69" s="14">
+        <v>560</v>
+      </c>
+      <c r="C69" s="14">
+        <v>55</v>
+      </c>
+      <c r="D69" s="14">
+        <v>140</v>
+      </c>
+      <c r="E69" s="14">
+        <v>75</v>
+      </c>
+      <c r="F69" s="14">
+        <v>300</v>
+      </c>
+      <c r="G69" s="14">
+        <v>6</v>
+      </c>
+      <c r="H69" s="14">
+        <v>35</v>
+      </c>
+      <c r="I69" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J69" s="15" t="str">
+        <v>1165</v>
+      </c>
+      <c r="J69" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K69" s="16"/>
-      <c r="L69" s="16"/>
-      <c r="M69" s="16"/>
-      <c r="N69" s="17"/>
+        <v>275</v>
+      </c>
+      <c r="K69" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="L69" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="M69" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N69" s="17" t="s">
+        <v>89</v>
+      </c>
     </row>
     <row r="70" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A70" s="13"/>
-      <c r="B70" s="14"/>
-      <c r="C70" s="14"/>
-      <c r="D70" s="14"/>
-      <c r="E70" s="14"/>
-      <c r="F70" s="14"/>
-      <c r="G70" s="14"/>
-      <c r="H70" s="14"/>
-      <c r="I70" s="15" t="str">
+      <c r="A70" s="13">
+        <v>46324</v>
+      </c>
+      <c r="B70" s="14">
+        <v>570</v>
+      </c>
+      <c r="C70" s="14">
+        <v>65</v>
+      </c>
+      <c r="D70" s="14">
+        <v>145</v>
+      </c>
+      <c r="E70" s="14">
+        <v>55</v>
+      </c>
+      <c r="F70" s="14">
+        <v>150</v>
+      </c>
+      <c r="G70" s="14">
+        <v>3</v>
+      </c>
+      <c r="H70" s="14">
+        <v>25</v>
+      </c>
+      <c r="I70" s="15">
         <f t="shared" ref="I70:I133" si="2">IF(SUM(B70:F70,H70)=0,"",SUM(B70:F70,H70))</f>
-        <v/>
-      </c>
-      <c r="J70" s="15" t="str">
+        <v>1010</v>
+      </c>
+      <c r="J70" s="15">
         <f t="shared" ref="J70:J133" si="3">IF(I70="","",1440-I70)</f>
-        <v/>
-      </c>
-      <c r="K70" s="16"/>
-      <c r="L70" s="16"/>
-      <c r="M70" s="16"/>
-      <c r="N70" s="17"/>
+        <v>430</v>
+      </c>
+      <c r="K70" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="L70" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="M70" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N70" s="17" t="s">
+        <v>69</v>
+      </c>
     </row>
     <row r="71" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A71" s="13"/>
